--- a/forms/app/moca_assessment.xlsx
+++ b/forms/app/moca_assessment.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:N140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,8 @@
           <t>Participant</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>field-list</t>
@@ -516,6 +518,12 @@
           <t>./source = 'user'</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -528,6 +536,17 @@
           <t>source</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -540,6 +559,17 @@
           <t>source_id</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -557,11 +587,20 @@
           <t>User</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -574,6 +613,17 @@
           <t>contact_id</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -586,6 +636,17 @@
           <t>name</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -593,6 +654,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -610,11 +683,20 @@
           <t>Participant</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -632,11 +714,20 @@
           <t>Select participant</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>select-contact type-participant</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -649,6 +740,17 @@
           <t>patient_id</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -661,6 +763,17 @@
           <t>name</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -673,6 +786,17 @@
           <t>age</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -685,6 +809,17 @@
           <t>gender</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -697,6 +832,17 @@
           <t>phone</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -709,6 +855,17 @@
           <t>education_level</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -721,6 +878,17 @@
           <t>consent_given</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -733,6 +901,17 @@
           <t>informant_name</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -745,6 +924,17 @@
           <t>informant_phone</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -752,6 +942,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -759,6 +961,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -771,11 +985,21 @@
           <t>patient_uuid</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>../inputs/contact/_id</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -788,11 +1012,21 @@
           <t>patient_id</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>../inputs/contact/patient_id</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -805,11 +1039,21 @@
           <t>patient_name</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>../inputs/contact/name</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -822,11 +1066,21 @@
           <t>patient_sex</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>../inputs/contact/gender</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -839,11 +1093,21 @@
           <t>patient_age</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>../inputs/contact/age</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -856,11 +1120,21 @@
           <t>patient_phone</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>../inputs/contact/phone</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -873,11 +1147,21 @@
           <t>patient_education</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>../inputs/contact/education_level</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -890,11 +1174,21 @@
           <t>screened_by</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>../inputs/user/contact_id</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -907,11 +1201,21 @@
           <t>screened_by_name</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>../inputs/user/name</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -929,11 +1233,20 @@
           <t>Consent</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -951,11 +1264,20 @@
           <t>Consent re-confirmed for the MoCA assessment?</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -963,6 +1285,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -980,6 +1314,8 @@
           <t>Visuospatial / Executive</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>field-list</t>
@@ -990,6 +1326,12 @@
           <t>${consent_reconfirmed} = 'yes'</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1007,6 +1349,16 @@
           <t>Please draw a line, going from a number to a letter in ascending order. Begin here [point to (1)] and draw a line from 1 then to A then to 2 and so on. End here [point to (E)].</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>trail_making.png</t>
@@ -1029,11 +1381,20 @@
           <t>Trail Making (1-A-2-B-3-C-4-D-5-E, no crossing lines)</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1051,6 +1412,16 @@
           <t>Copy this drawing as accurately as you can, in the space below.</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>cube.png</t>
@@ -1073,11 +1444,20 @@
           <t>Cube Copy (3D, all lines, no extra lines, parallel lines)</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1095,6 +1475,16 @@
           <t>Draw a clock. Put in all the numbers and set the time to 10 past 11.</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1112,11 +1502,20 @@
           <t>Clock - Contour (circle, minor distortion OK)</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1134,11 +1533,20 @@
           <t>Clock - Numbers (all 12 present, correct order, correct quadrants)</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1156,11 +1564,20 @@
           <t>Clock - Hands (two hands, 10:11, hour hand shorter, centered)</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1168,6 +1585,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1185,6 +1614,8 @@
           <t>Naming</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>field-list</t>
@@ -1195,6 +1626,12 @@
           <t>${consent_reconfirmed} = 'yes'</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1212,6 +1649,16 @@
           <t>Beginning on the left, point to each figure and say: Tell me the name of this animal.</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>naming.png</t>
@@ -1234,11 +1681,20 @@
           <t>Figure 1 (Lion)</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1256,11 +1712,20 @@
           <t>Figure 2 (Rhinoceros / Rhino)</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1278,11 +1743,20 @@
           <t>Figure 3 (Camel / Dromedary)</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1290,6 +1764,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1307,6 +1793,8 @@
           <t>Memory</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>field-list</t>
@@ -1317,6 +1805,12 @@
           <t>${consent_reconfirmed} = 'yes'</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1334,6 +1828,16 @@
           <t>This is a memory test. I am going to read a list of words that you will have to remember now and later on. Listen carefully. When I am through, tell me as many words as you can remember. It does not matter in what order you say them.</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1351,6 +1855,17 @@
           <t>Words: FACE, VELVET, CHURCH, DAISY, RED</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1368,11 +1883,20 @@
           <t>Trial 1</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1390,11 +1914,20 @@
           <t>FACE</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1412,11 +1945,20 @@
           <t>VELVET</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1434,11 +1976,20 @@
           <t>CHURCH</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1456,11 +2007,20 @@
           <t>DAISY</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1478,11 +2038,20 @@
           <t>RED</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1490,6 +2059,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1507,6 +2088,16 @@
           <t>I am going to read the same list for a second time. Try to remember and tell me as many words as you can, including words you said the first time.</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1524,11 +2115,20 @@
           <t>Trial 2</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1546,11 +2146,20 @@
           <t>FACE</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1568,11 +2177,20 @@
           <t>VELVET</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1590,11 +2208,20 @@
           <t>CHURCH</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1612,11 +2239,20 @@
           <t>DAISY</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1634,11 +2270,20 @@
           <t>RED</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1646,6 +2291,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1663,6 +2320,16 @@
           <t>I will ask you to recall those words again at the end of the test.</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1670,6 +2337,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1687,6 +2366,8 @@
           <t>Attention</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>field-list</t>
@@ -1697,6 +2378,12 @@
           <t>${consent_reconfirmed} = 'yes'</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1714,6 +2401,16 @@
           <t>I am going to say some numbers and when I am through, repeat them to me exactly as I said them. Sequence: 2 1 8 5 4 (1 digit/sec).</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1731,11 +2428,20 @@
           <t>Forward Digit Span (2-1-8-5-4) correct?</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1753,6 +2459,16 @@
           <t>Now I am going to say some more numbers, but when I am through you must repeat them to me in the backwards order. Sequence: 7 4 2 (1 digit/sec). Correct backward: 2-4-7.</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1770,11 +2486,20 @@
           <t>Backward Digit Span (2-4-7) correct?</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1792,6 +2517,16 @@
           <t>I am going to read a sequence of letters. Every time I say the letter A, tap your hand once. If I say a different letter, do not tap your hand. Letters: F B A C M N A A J K L B A F A K D E A A A J A M O F A A B (read at 1/sec).</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1809,11 +2544,20 @@
           <t>Vigilance (A-tapping) - 0 or 1 error?</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1831,6 +2575,16 @@
           <t>Count by subtracting seven from 100, and then keep subtracting seven from your answer until I tell you to stop. (Max 5 subtractions: 93, 86, 79, 72, 65)</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1848,11 +2602,20 @@
           <t>Serial 7s score (0-3)</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1860,6 +2623,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1877,6 +2652,8 @@
           <t>Language</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>field-list</t>
@@ -1887,6 +2664,12 @@
           <t>${consent_reconfirmed} = 'yes'</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1904,6 +2687,16 @@
           <t>Repeat: I only know that John is the one to help today. (Must be exact)</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1921,11 +2714,20 @@
           <t>Sentence 1: I only know that John is the one to help today. (Exact)</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1943,6 +2745,16 @@
           <t>The cat always hid under the couch when dogs were in the room. (Must be exact)</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1960,11 +2772,20 @@
           <t>Sentence 2: The cat always hid under the couch when dogs were in the room. (Exact)</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1982,6 +2803,16 @@
           <t>Tell me as many words as you can think of that begin with the letter F. No proper nouns, numbers, or same-sound-different-suffix words. 60 seconds.</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1999,16 +2830,25 @@
           <t>Fluency count (F words, &gt;=11 = 1 pt)</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>. &gt;= 0</t>
         </is>
       </c>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2016,6 +2856,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2033,6 +2885,8 @@
           <t>Abstraction</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>field-list</t>
@@ -2043,6 +2897,12 @@
           <t>${consent_reconfirmed} = 'yes'</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2060,6 +2920,16 @@
           <t>Practice: Tell me how an orange and a banana are alike. If concrete, prompt once: Tell me another way. If not fruit, say: Yes, and they are also both fruit.</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2077,11 +2947,20 @@
           <t>Train - Bicycle (conceptual: transportation/travelling/trips = 1 pt; wheels = 0)</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2099,11 +2978,20 @@
           <t>Ruler - Watch (conceptual: measuring instruments/measure = 1 pt; numbers = 0)</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2111,6 +2999,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2128,6 +3028,8 @@
           <t>Delayed Recall</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>field-list</t>
@@ -2138,6 +3040,12 @@
           <t>${consent_reconfirmed} = 'yes'</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2155,6 +3063,16 @@
           <t>I read some words to you earlier, which I asked you to remember. Tell me as many of those words as you can remember.</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2172,11 +3090,20 @@
           <t>FACE (free recall)</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2194,6 +3121,16 @@
           <t>FACE - Category cue (part of body)</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2211,6 +3148,16 @@
           <t>FACE - Multiple choice (nose/face/hand)</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2228,11 +3175,20 @@
           <t>VELVET (free recall)</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2250,6 +3206,16 @@
           <t>VELVET - Category cue (type of fabric)</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2267,6 +3233,16 @@
           <t>VELVET - Multiple choice (denim/cotton/velvet)</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2284,11 +3260,20 @@
           <t>CHURCH (free recall)</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2306,6 +3291,16 @@
           <t>CHURCH - Category cue (type of building)</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2323,6 +3318,16 @@
           <t>CHURCH - Multiple choice (church/school/hospital)</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2340,11 +3345,20 @@
           <t>DAISY (free recall)</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2362,6 +3376,16 @@
           <t>DAISY - Category cue (type of flower)</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2379,6 +3403,16 @@
           <t>DAISY - Multiple choice (rose/daisy/tulip)</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2396,11 +3430,20 @@
           <t>RED (free recall)</t>
         </is>
       </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2418,6 +3461,16 @@
           <t>RED - Category cue (a colour)</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2435,6 +3488,16 @@
           <t>RED - Multiple choice (red/blue/green)</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2442,6 +3505,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2459,6 +3534,8 @@
           <t>Orientation</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>field-list</t>
@@ -2469,6 +3546,12 @@
           <t>${consent_reconfirmed} = 'yes'</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2486,6 +3569,16 @@
           <t>Tell me the date today. If incomplete, prompt for year, month, exact date, day. Then: Tell me the name of this place, and which city it is in. No points if off by one day.</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2503,11 +3596,20 @@
           <t>Exact date correct?</t>
         </is>
       </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2525,11 +3627,20 @@
           <t>Month correct?</t>
         </is>
       </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2547,11 +3658,20 @@
           <t>Year correct?</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2569,11 +3689,20 @@
           <t>Day of week correct?</t>
         </is>
       </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2591,11 +3720,20 @@
           <t>Place (hospital/clinic/office) correct?</t>
         </is>
       </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2613,11 +3751,20 @@
           <t>City correct?</t>
         </is>
       </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2625,6 +3772,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2637,11 +3796,21 @@
           <t>moca_visuospatial_total</t>
         </is>
       </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
           <t>if(${trail_making} = "yes", 1, 0) + if(${cube_copy} = "yes", 1, 0) + if(${clock_contour} = "yes", 1, 0) + if(${clock_numbers} = "yes", 1, 0) + if(${clock_hands} = "yes", 1, 0)</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2654,11 +3823,21 @@
           <t>moca_naming_total</t>
         </is>
       </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
           <t>if(${naming_1} = "yes", 1, 0) + if(${naming_2} = "yes", 1, 0) + if(${naming_3} = "yes", 1, 0)</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2671,11 +3850,21 @@
           <t>moca_memory_total</t>
         </is>
       </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
           <t>if(${delayed_face} = "yes", 1, 0) + if(${delayed_velvet} = "yes", 1, 0) + if(${delayed_church} = "yes", 1, 0) + if(${delayed_daisy} = "yes", 1, 0) + if(${delayed_red} = "yes", 1, 0)</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2688,11 +3877,21 @@
           <t>moca_attention_total</t>
         </is>
       </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
           <t>if(${digit_span_fwd} = "yes", 1, 0) + if(${digit_span_bwd} = "yes", 1, 0) + if(${vigilance} = "yes", 1, 0) + ${serial_7s}</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2705,11 +3904,21 @@
           <t>moca_language_total</t>
         </is>
       </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
           <t>if(${sentence_rep_1} = "yes", 1, 0) + if(${sentence_rep_2} = "yes", 1, 0) + if(${fluency_count} &gt;= 11, 1, 0)</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2722,11 +3931,21 @@
           <t>moca_abstraction_total</t>
         </is>
       </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>if(${abstraction_1} = "yes", 1, 0) + if(${abstraction_2} = "yes", 1, 0)</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2739,11 +3958,21 @@
           <t>moca_delayed_total</t>
         </is>
       </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>if(${delayed_face} = "yes", 1, 0) + if(${delayed_velvet} = "yes", 1, 0) + if(${delayed_church} = "yes", 1, 0) + if(${delayed_daisy} = "yes", 1, 0) + if(${delayed_red} = "yes", 1, 0)</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2756,11 +3985,21 @@
           <t>moca_orientation_total</t>
         </is>
       </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
           <t>if(${orientation_date} = "yes", 1, 0) + if(${orientation_month} = "yes", 1, 0) + if(${orientation_year} = "yes", 1, 0) + if(${orientation_day} = "yes", 1, 0) + if(${orientation_place} = "yes", 1, 0) + if(${orientation_city} = "yes", 1, 0)</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2773,11 +4012,21 @@
           <t>moca_raw_total</t>
         </is>
       </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>${moca_visuospatial_total} + ${moca_naming_total} + ${moca_memory_total} + ${moca_attention_total} + ${moca_language_total} + ${moca_abstraction_total} + ${moca_orientation_total}</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2790,11 +4039,21 @@
           <t>moca_education_adj</t>
         </is>
       </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>if(${patient_education} = "illiterate" or ${patient_education} = "primary", 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${patient_education} = "illiterate" or ${patient_education} = "primary" or ${patient_education} = "8th" or ${patient_education} = "10th" or ${patient_education} = "12th", 1, 0)</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2807,11 +4066,21 @@
           <t>moca_total_score</t>
         </is>
       </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>min(${moca_raw_total} + ${moca_education_adj}, 30)</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2824,11 +4093,21 @@
           <t>moca_interpretation</t>
         </is>
       </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>if(${moca_total_score} &gt;= 26, "normal", "impaired")</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2846,11 +4125,20 @@
           <t>Administrator</t>
         </is>
       </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2868,11 +4156,20 @@
           <t>Administered by (staff name)</t>
         </is>
       </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2890,6 +4187,12 @@
           <t>Date &amp; Time of Assessment</t>
         </is>
       </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2900,6 +4203,8 @@
           <t>now()</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2907,6 +4212,18 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2924,11 +4241,20 @@
           <t>MoCA sheet / supporting documents</t>
         </is>
       </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2951,33 +4277,45 @@
           <t>Upload the completed paper MoCA sheet (image or PDF). Add more than one if needed.</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>file</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>moca_image</t>
+          <t>moca_sheet</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Upload MoCA sheet (image)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Upload clear photo of MoCA sheet. Accepts JPG, JPEG, PNG.</t>
-        </is>
-      </c>
+          <t>Upload MoCA sheet (image or PDF)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
           <t>binary</t>
@@ -2987,43 +4325,40 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>moca_pdf</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Upload MoCA sheet (PDF)</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Upload PDF of MoCA sheet. Accepts PDF.</t>
-        </is>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>binary</t>
-        </is>
-      </c>
+          <t>end repeat</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>end repeat</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
           <t>end group</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
